--- a/ZonasEscolares/excels/JUNIN-HUANCAYO-EL_TAMBO.xlsx
+++ b/ZonasEscolares/excels/JUNIN-HUANCAYO-EL_TAMBO.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EL_TAMBO</t>
+          <t>EL TAMBO</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EL_TAMBO</t>
+          <t>EL TAMBO</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EL_TAMBO</t>
+          <t>EL TAMBO</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EL_TAMBO</t>
+          <t>EL TAMBO</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -716,7 +716,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EL_TAMBO</t>
+          <t>EL TAMBO</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -768,7 +768,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EL_TAMBO</t>
+          <t>EL TAMBO</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EL_TAMBO</t>
+          <t>EL TAMBO</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EL_TAMBO</t>
+          <t>EL TAMBO</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EL_TAMBO</t>
+          <t>EL TAMBO</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EL_TAMBO</t>
+          <t>EL TAMBO</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EL_TAMBO</t>
+          <t>EL TAMBO</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>EL_TAMBO</t>
+          <t>EL TAMBO</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>EL_TAMBO</t>
+          <t>EL TAMBO</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>EL_TAMBO</t>
+          <t>EL TAMBO</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>EL_TAMBO</t>
+          <t>EL TAMBO</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>EL_TAMBO</t>
+          <t>EL TAMBO</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>EL_TAMBO</t>
+          <t>EL TAMBO</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>EL_TAMBO</t>
+          <t>EL TAMBO</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>EL_TAMBO</t>
+          <t>EL TAMBO</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>EL_TAMBO</t>
+          <t>EL TAMBO</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>EL_TAMBO</t>
+          <t>EL TAMBO</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>EL_TAMBO</t>
+          <t>EL TAMBO</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>EL_TAMBO</t>
+          <t>EL TAMBO</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>EL_TAMBO</t>
+          <t>EL TAMBO</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>EL_TAMBO</t>
+          <t>EL TAMBO</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>EL_TAMBO</t>
+          <t>EL TAMBO</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>EL_TAMBO</t>
+          <t>EL TAMBO</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>EL_TAMBO</t>
+          <t>EL TAMBO</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>EL_TAMBO</t>
+          <t>EL TAMBO</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>EL_TAMBO</t>
+          <t>EL TAMBO</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>EL_TAMBO</t>
+          <t>EL TAMBO</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>EL_TAMBO</t>
+          <t>EL TAMBO</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>EL_TAMBO</t>
+          <t>EL TAMBO</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>EL_TAMBO</t>
+          <t>EL TAMBO</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2276,7 +2276,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>EL_TAMBO</t>
+          <t>EL TAMBO</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>EL_TAMBO</t>
+          <t>EL TAMBO</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>EL_TAMBO</t>
+          <t>EL TAMBO</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>EL_TAMBO</t>
+          <t>EL TAMBO</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>EL_TAMBO</t>
+          <t>EL TAMBO</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>EL_TAMBO</t>
+          <t>EL TAMBO</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>EL_TAMBO</t>
+          <t>EL TAMBO</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>EL_TAMBO</t>
+          <t>EL TAMBO</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>EL_TAMBO</t>
+          <t>EL TAMBO</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>EL_TAMBO</t>
+          <t>EL TAMBO</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>EL_TAMBO</t>
+          <t>EL TAMBO</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>EL_TAMBO</t>
+          <t>EL TAMBO</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>EL_TAMBO</t>
+          <t>EL TAMBO</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>EL_TAMBO</t>
+          <t>EL TAMBO</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>EL_TAMBO</t>
+          <t>EL TAMBO</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>EL_TAMBO</t>
+          <t>EL TAMBO</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>EL_TAMBO</t>
+          <t>EL TAMBO</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>EL_TAMBO</t>
+          <t>EL TAMBO</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/JUNIN-HUANCAYO-EL_TAMBO.xlsx
+++ b/ZonasEscolares/excels/JUNIN-HUANCAYO-EL_TAMBO.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>ICTUS CRISTO SALVADOR</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-12.06543</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-75.22152</v>
-      </c>
-      <c r="I2" t="n">
-        <v>202</v>
-      </c>
-      <c r="J2" t="n">
-        <v>16</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-12.06543</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-75.22152</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>LUIS AGUILAR ROMANI</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-12.05671</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-75.23399999999999</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1003</v>
-      </c>
-      <c r="J3" t="n">
-        <v>101</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-12.05671</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-75.234</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>255 MI PEQUEÑO MUNDO</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-12.0567</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-75.2246</v>
-      </c>
-      <c r="I4" t="n">
-        <v>280</v>
-      </c>
-      <c r="J4" t="n">
-        <v>14</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-12.0567</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-75.2246</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>30211</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-12.0218</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-75.2332</v>
-      </c>
-      <c r="I5" t="n">
-        <v>350</v>
-      </c>
-      <c r="J5" t="n">
-        <v>17</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-12.0218</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-75.2332</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>643</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-12.0497</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-75.2146</v>
-      </c>
-      <c r="I6" t="n">
-        <v>28</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-12.0497</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-75.2146</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>30213 / 30213 JUAN LUCIO SOTO JEREMIAS</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-12.0618</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-75.2302</v>
-      </c>
-      <c r="I7" t="n">
-        <v>333</v>
-      </c>
-      <c r="J7" t="n">
-        <v>18</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-12.0618</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-75.2302</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>333</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>30216 SAGRADO CORAZON DE MARIA</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-12.0607</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-75.218</v>
-      </c>
-      <c r="I8" t="n">
-        <v>560</v>
-      </c>
-      <c r="J8" t="n">
-        <v>31</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-12.0607</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-75.218</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>560</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>30218 MADRE TERESA DE CALCUTA</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-12.03745</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-75.22306</v>
-      </c>
-      <c r="I9" t="n">
-        <v>266</v>
-      </c>
-      <c r="J9" t="n">
-        <v>15</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-12.03745</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-75.22306</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>30224 / 30224 CORAZON DE JESUS</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-12.0534</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-75.2085</v>
-      </c>
-      <c r="I10" t="n">
-        <v>391</v>
-      </c>
-      <c r="J10" t="n">
-        <v>25</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-12.0534</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-75.2085</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>391</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>30225 LA ALBORADA</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-12.0469</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-75.2281</v>
-      </c>
-      <c r="I11" t="n">
-        <v>580</v>
-      </c>
-      <c r="J11" t="n">
-        <v>31</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-12.0469</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-75.2281</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>580</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>30226 NUESTRA SRA.DE FATIMA</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-12.06378</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-75.22582</v>
-      </c>
-      <c r="I12" t="n">
-        <v>457</v>
-      </c>
-      <c r="J12" t="n">
-        <v>29</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-12.06378</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-75.22582</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>457</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>30426 VIRGEN DE LA MERCED</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-12.0424</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-75.22069999999999</v>
-      </c>
-      <c r="I13" t="n">
-        <v>299</v>
-      </c>
-      <c r="J13" t="n">
-        <v>15</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-12.0424</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-75.2207</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>31510 VIRGEN DE FATIMA</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-12.04921</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-75.22696999999999</v>
-      </c>
-      <c r="I14" t="n">
-        <v>338</v>
-      </c>
-      <c r="J14" t="n">
-        <v>24</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-12.04921</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-75.22697</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>338</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>31593 JAVIER HERAUD</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-12.05511</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-75.23259</v>
-      </c>
-      <c r="I15" t="n">
-        <v>394</v>
-      </c>
-      <c r="J15" t="n">
-        <v>31</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-12.05511</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-75.23259</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>394</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>31594</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-12.04798</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-75.21387</v>
-      </c>
-      <c r="I16" t="n">
-        <v>417</v>
-      </c>
-      <c r="J16" t="n">
-        <v>24</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-12.04798</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-75.21387</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>417</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>31942 MARISCAL CASTILLA</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-12.05833</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-75.21809</v>
-      </c>
-      <c r="I17" t="n">
-        <v>496</v>
-      </c>
-      <c r="J17" t="n">
-        <v>22</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-12.05833</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-75.21809</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>496</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>MICAELA BASTIDAS</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-12.0503</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-75.22929999999999</v>
-      </c>
-      <c r="I18" t="n">
-        <v>600</v>
-      </c>
-      <c r="J18" t="n">
-        <v>32</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-12.0503</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-75.2293</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>FRANCISCO DE ZELA</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-12.038</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-75.2225</v>
-      </c>
-      <c r="I19" t="n">
-        <v>258</v>
-      </c>
-      <c r="J19" t="n">
-        <v>23</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-12.038</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-75.2225</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>JOSE FAUSTINO SANCHEZ CARRION</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-12.0273</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-75.22915999999999</v>
-      </c>
-      <c r="I20" t="n">
-        <v>276</v>
-      </c>
-      <c r="J20" t="n">
-        <v>26</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-12.0273</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-75.22916</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>LA VICTORIA</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-12.02835</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-75.23743</v>
-      </c>
-      <c r="I21" t="n">
-        <v>700</v>
-      </c>
-      <c r="J21" t="n">
-        <v>37</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-12.02835</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-75.23743</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>POLITECNICO REGIONAL DEL CENTRO</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-12.06216</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-75.21608000000001</v>
-      </c>
-      <c r="I22" t="n">
-        <v>2318</v>
-      </c>
-      <c r="J22" t="n">
-        <v>152</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-12.06216</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-75.21608</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2318</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>HEROES DEL CENEPA</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-12.01819</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-75.22348</v>
-      </c>
-      <c r="I23" t="n">
-        <v>251</v>
-      </c>
-      <c r="J23" t="n">
-        <v>20</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-12.01819</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-75.22348</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>NUESTRA SEÑORA DE FATIMA</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-12.0633</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-75.22601</v>
-      </c>
-      <c r="I24" t="n">
-        <v>446</v>
-      </c>
-      <c r="J24" t="n">
-        <v>27</v>
-      </c>
-      <c r="K24" t="n">
-        <v>2</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-12.0633</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-75.22601</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>446</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>30129 MICAELA BASTIDAS</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-12.05126</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-75.2092</v>
-      </c>
-      <c r="I25" t="n">
-        <v>411</v>
-      </c>
-      <c r="J25" t="n">
-        <v>29</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-12.05126</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-75.2092</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>411</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1769,20 +1997,30 @@
           <t>EMILIA BARCIA BONIFFATTI</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-12.0648</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-75.21939</v>
-      </c>
-      <c r="I26" t="n">
-        <v>220</v>
-      </c>
-      <c r="J26" t="n">
-        <v>14</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-12.0648</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-75.21939</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1821,20 +2059,30 @@
           <t>CONVENIO ANDRES BELLO</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-12.04251</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-75.22614</v>
-      </c>
-      <c r="I27" t="n">
-        <v>731</v>
-      </c>
-      <c r="J27" t="n">
-        <v>36</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-12.04251</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-75.22614</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>731</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1873,20 +2121,30 @@
           <t>GERMINAL</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-12.06585</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-75.22018</v>
-      </c>
-      <c r="I28" t="n">
-        <v>494</v>
-      </c>
-      <c r="J28" t="n">
-        <v>12</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-12.06585</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-75.22018</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>494</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1925,20 +2183,30 @@
           <t>PRAXIS LA ESPERANZA</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>-12.03078</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-75.22663</v>
-      </c>
-      <c r="I29" t="n">
-        <v>975</v>
-      </c>
-      <c r="J29" t="n">
-        <v>35</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-12.03078</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-75.22663</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>975</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1977,20 +2245,30 @@
           <t>PAMER</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>-12.04904</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-75.22534</v>
-      </c>
-      <c r="I30" t="n">
-        <v>795</v>
-      </c>
-      <c r="J30" t="n">
-        <v>38</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-12.04904</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-75.22534</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>795</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2029,20 +2307,30 @@
           <t>COSMOS</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>-12.05454</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-75.21288</v>
-      </c>
-      <c r="I31" t="n">
-        <v>12</v>
-      </c>
-      <c r="J31" t="n">
-        <v>5</v>
-      </c>
-      <c r="K31" t="n">
-        <v>1</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-12.05454</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-75.21288</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2081,20 +2369,30 @@
           <t>GELICICH</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>-12.063345</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-75.213314</v>
-      </c>
-      <c r="I32" t="n">
-        <v>614</v>
-      </c>
-      <c r="J32" t="n">
-        <v>43</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-12.063345</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-75.213314</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>614</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2133,20 +2431,30 @@
           <t>SALESIANO SANTA ROSA</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>-12.06624</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-75.215</v>
-      </c>
-      <c r="I33" t="n">
-        <v>1145</v>
-      </c>
-      <c r="J33" t="n">
-        <v>44</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-12.06624</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-75.215</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1145</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2185,20 +2493,30 @@
           <t>SAN PIO X</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>-12.04182</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-75.21626999999999</v>
-      </c>
-      <c r="I34" t="n">
-        <v>308</v>
-      </c>
-      <c r="J34" t="n">
-        <v>26</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-12.04182</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-75.21627</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2237,20 +2555,30 @@
           <t>HABICH</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>-12.02946</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-75.23436</v>
-      </c>
-      <c r="I35" t="n">
-        <v>212</v>
-      </c>
-      <c r="J35" t="n">
-        <v>21</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-12.02946</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-75.23436</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2289,20 +2617,30 @@
           <t>INGENIERIA</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>-12.064007</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-75.213252</v>
-      </c>
-      <c r="I36" t="n">
-        <v>1840</v>
-      </c>
-      <c r="J36" t="n">
-        <v>66</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-12.064007</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-75.213252</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1840</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2341,20 +2679,30 @@
           <t>SAN ANTONIO MARIA CLARET</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>-12.05754</v>
-      </c>
-      <c r="H37" t="n">
-        <v>-75.217269</v>
-      </c>
-      <c r="I37" t="n">
-        <v>842</v>
-      </c>
-      <c r="J37" t="n">
-        <v>46</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-12.05754</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-75.217269</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>842</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2393,20 +2741,30 @@
           <t>SALESIANO DON BOSCO</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>-12.06793</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-75.21709</v>
-      </c>
-      <c r="I38" t="n">
-        <v>691</v>
-      </c>
-      <c r="J38" t="n">
-        <v>47</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-12.06793</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-75.21709</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>691</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2445,20 +2803,30 @@
           <t>MAESTRO REDENTOR</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>-12.06205</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-75.21411999999999</v>
-      </c>
-      <c r="I39" t="n">
-        <v>261</v>
-      </c>
-      <c r="J39" t="n">
-        <v>25</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-12.06205</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-75.21412</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2497,20 +2865,30 @@
           <t>LAS CARMELITAS</t>
         </is>
       </c>
-      <c r="G40" t="n">
-        <v>-12.04338</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-75.23135000000001</v>
-      </c>
-      <c r="I40" t="n">
-        <v>218</v>
-      </c>
-      <c r="J40" t="n">
-        <v>10</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-12.04338</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-75.23135</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2549,20 +2927,30 @@
           <t>SOFFIANHUM</t>
         </is>
       </c>
-      <c r="G41" t="n">
-        <v>-12.06176</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-75.22644</v>
-      </c>
-      <c r="I41" t="n">
-        <v>44</v>
-      </c>
-      <c r="J41" t="n">
-        <v>3</v>
-      </c>
-      <c r="K41" t="n">
-        <v>2</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-12.06176</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-75.22644</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2601,20 +2989,30 @@
           <t>INTEGRACION</t>
         </is>
       </c>
-      <c r="G42" t="n">
-        <v>-12.05177</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-75.21006</v>
-      </c>
-      <c r="I42" t="n">
-        <v>204</v>
-      </c>
-      <c r="J42" t="n">
-        <v>3</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-12.05177</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>-75.21006</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2653,20 +3051,30 @@
           <t>SOFFIANHUM</t>
         </is>
       </c>
-      <c r="G43" t="n">
-        <v>-12.06177</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-75.22642999999999</v>
-      </c>
-      <c r="I43" t="n">
-        <v>51</v>
-      </c>
-      <c r="J43" t="n">
-        <v>5</v>
-      </c>
-      <c r="K43" t="n">
-        <v>2</v>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-12.06177</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>-75.22643</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -2705,20 +3113,30 @@
           <t>WINNER BOYS</t>
         </is>
       </c>
-      <c r="G44" t="n">
-        <v>-12.04498</v>
-      </c>
-      <c r="H44" t="n">
-        <v>-75.21402999999999</v>
-      </c>
-      <c r="I44" t="n">
-        <v>558</v>
-      </c>
-      <c r="J44" t="n">
-        <v>15</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-12.04498</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>-75.21403</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>558</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -2757,20 +3175,30 @@
           <t>31508 SIMON BOLIVAR</t>
         </is>
       </c>
-      <c r="G45" t="n">
-        <v>-12.05188</v>
-      </c>
-      <c r="H45" t="n">
-        <v>-75.23397</v>
-      </c>
-      <c r="I45" t="n">
-        <v>365</v>
-      </c>
-      <c r="J45" t="n">
-        <v>21</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-12.05188</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>-75.23397</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>365</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -2809,20 +3237,30 @@
           <t>31557 CAHUIDE</t>
         </is>
       </c>
-      <c r="G46" t="n">
-        <v>-12.0339</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-75.2272</v>
-      </c>
-      <c r="I46" t="n">
-        <v>256</v>
-      </c>
-      <c r="J46" t="n">
-        <v>12</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-12.0339</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>-75.2272</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -2861,20 +3299,30 @@
           <t>LATINO INNOVA E.I.R.L.</t>
         </is>
       </c>
-      <c r="G47" t="n">
-        <v>-12.03116</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-75.22790000000001</v>
-      </c>
-      <c r="I47" t="n">
-        <v>289</v>
-      </c>
-      <c r="J47" t="n">
-        <v>18</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-12.03116</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>-75.2279</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -2913,20 +3361,30 @@
           <t>TRILCE</t>
         </is>
       </c>
-      <c r="G48" t="n">
-        <v>-12.06588</v>
-      </c>
-      <c r="H48" t="n">
-        <v>-75.22163999999999</v>
-      </c>
-      <c r="I48" t="n">
-        <v>621</v>
-      </c>
-      <c r="J48" t="n">
-        <v>23</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-12.06588</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>-75.22164</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>621</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -2965,20 +3423,30 @@
           <t>INGENIERIA INTERNACIONAL</t>
         </is>
       </c>
-      <c r="G49" t="n">
-        <v>-12.05424</v>
-      </c>
-      <c r="H49" t="n">
-        <v>-75.21679</v>
-      </c>
-      <c r="I49" t="n">
-        <v>222</v>
-      </c>
-      <c r="J49" t="n">
-        <v>26</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-12.05424</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>-75.21679</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -3017,20 +3485,30 @@
           <t>PRAXIS LAS ESTRELLAS</t>
         </is>
       </c>
-      <c r="G50" t="n">
-        <v>-12.02733</v>
-      </c>
-      <c r="H50" t="n">
-        <v>-75.23433</v>
-      </c>
-      <c r="I50" t="n">
-        <v>949</v>
-      </c>
-      <c r="J50" t="n">
-        <v>21</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-12.02733</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>-75.23433</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>949</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -3069,20 +3547,30 @@
           <t>SEMILLITAS DE HORIZONTE</t>
         </is>
       </c>
-      <c r="G51" t="n">
-        <v>-12.05074</v>
-      </c>
-      <c r="H51" t="n">
-        <v>-75.21549</v>
-      </c>
-      <c r="I51" t="n">
-        <v>43</v>
-      </c>
-      <c r="J51" t="n">
-        <v>2</v>
-      </c>
-      <c r="K51" t="n">
-        <v>1</v>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-12.05074</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>-75.21549</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -3121,20 +3609,30 @@
           <t>HARVARD</t>
         </is>
       </c>
-      <c r="G52" t="n">
-        <v>-12.052298</v>
-      </c>
-      <c r="H52" t="n">
-        <v>-75.224459</v>
-      </c>
-      <c r="I52" t="n">
-        <v>699</v>
-      </c>
-      <c r="J52" t="n">
-        <v>36</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0</v>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-12.052298</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>-75.224459</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>699</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -3173,20 +3671,30 @@
           <t>EXCELENTI</t>
         </is>
       </c>
-      <c r="G53" t="n">
-        <v>-12.06047</v>
-      </c>
-      <c r="H53" t="n">
-        <v>-75.21357</v>
-      </c>
-      <c r="I53" t="n">
-        <v>705</v>
-      </c>
-      <c r="J53" t="n">
-        <v>15</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>-12.06047</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>-75.21357</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/JUNIN-HUANCAYO-EL_TAMBO.xlsx
+++ b/ZonasEscolares/excels/JUNIN-HUANCAYO-EL_TAMBO.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>221266</t>
+          <t>236809</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ICTUS CRISTO SALVADOR</t>
+          <t>LAS CARMELITAS</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-12.06543</t>
+          <t>-12.04338</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-75.22152</t>
+          <t>-75.23135</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>218</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>222708</t>
+          <t>223492</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>255 MI PEQUEÑO MUNDO</t>
+          <t>GERMINAL</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-12.0567</t>
+          <t>-12.06585</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-75.2246</t>
+          <t>-75.22018</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>494</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>222727</t>
+          <t>641516</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>30211</t>
+          <t>31557 CAHUIDE</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-12.0218</t>
+          <t>-12.0339</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-75.2332</t>
+          <t>-75.2272</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>256</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,37 +749,37 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>222850</t>
+          <t>222708</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>255 MI PEQUEÑO MUNDO</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-12.0497</t>
+          <t>-12.0567</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-75.2146</t>
+          <t>-75.2246</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>280</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>222930</t>
+          <t>223374</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>30213 / 30213 JUAN LUCIO SOTO JEREMIAS</t>
+          <t>EMILIA BARCIA BONIFFATTI</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-12.0618</t>
+          <t>-12.0648</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-75.2302</t>
+          <t>-75.21939</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>220</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>222968</t>
+          <t>222987</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>30216 SAGRADO CORAZON DE MARIA</t>
+          <t>30218 MADRE TERESA DE CALCUTA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-12.0607</t>
+          <t>-12.03745</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-75.218</t>
+          <t>-75.22306</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>266</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,27 +935,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>222987</t>
+          <t>223072</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>30218 MADRE TERESA DE CALCUTA</t>
+          <t>30426 VIRGEN DE LA MERCED</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-12.03745</t>
+          <t>-12.0424</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-75.22306</t>
+          <t>-75.2207</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>299</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>223029</t>
+          <t>641093</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>30224 / 30224 CORAZON DE JESUS</t>
+          <t>WINNER BOYS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-12.0534</t>
+          <t>-12.04498</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-75.2085</t>
+          <t>-75.21403</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>558</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>223034</t>
+          <t>848531</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>30225 LA ALBORADA</t>
+          <t>EXCELENTI</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-12.0469</t>
+          <t>-12.06047</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-75.2281</t>
+          <t>-75.21357</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>705</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>223048</t>
+          <t>223251</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>30226 NUESTRA SRA.DE FATIMA</t>
+          <t>POLITECNICO REGIONAL DEL CENTRO</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-12.06378</t>
+          <t>-12.06216</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-75.22582</t>
+          <t>-75.21608</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>457</t>
+          <t>2318</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>152</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>223072</t>
+          <t>221266</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>30426 VIRGEN DE LA MERCED</t>
+          <t>ICTUS CRISTO SALVADOR</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-12.0424</t>
+          <t>-12.06543</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-75.2207</t>
+          <t>-75.22152</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>202</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>223091</t>
+          <t>222727</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>31510 VIRGEN DE FATIMA</t>
+          <t>30211</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-12.04921</t>
+          <t>-12.0218</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-75.22697</t>
+          <t>-75.2332</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>350</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>223114</t>
+          <t>222930</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>31593 JAVIER HERAUD</t>
+          <t>30213 / 30213 JUAN LUCIO SOTO JEREMIAS</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-12.05511</t>
+          <t>-12.0618</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-75.23259</t>
+          <t>-75.2302</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>333</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>223128</t>
+          <t>642361</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>31594</t>
+          <t>LATINO INNOVA E.I.R.L.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-12.04798</t>
+          <t>-12.03116</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-75.21387</t>
+          <t>-75.2279</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>417</t>
+          <t>289</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,37 +1431,37 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>223152</t>
+          <t>222850</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>31942 MARISCAL CASTILLA</t>
+          <t>643</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-12.05833</t>
+          <t>-12.0497</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-75.21809</t>
+          <t>-75.2146</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>496</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1493,37 +1493,37 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>223190</t>
+          <t>835152</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MICAELA BASTIDAS</t>
+          <t>SEMILLITAS DE HORIZONTE</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-12.0503</t>
+          <t>-12.05074</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-75.2293</t>
+          <t>-75.21549</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>223208</t>
+          <t>223289</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>FRANCISCO DE ZELA</t>
+          <t>HEROES DEL CENEPA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-12.038</t>
+          <t>-12.01819</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-75.2225</t>
+          <t>-75.22348</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>251</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>223213</t>
+          <t>224000</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>JOSE FAUSTINO SANCHEZ CARRION</t>
+          <t>HABICH</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-12.0273</t>
+          <t>-12.02946</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-75.22916</t>
+          <t>-75.23436</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>212</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>223232</t>
+          <t>641494</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>LA VICTORIA</t>
+          <t>31508 SIMON BOLIVAR</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-12.02835</t>
+          <t>-12.05188</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-75.23743</t>
+          <t>-75.23397</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>365</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>223251</t>
+          <t>779844</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>POLITECNICO REGIONAL DEL CENTRO</t>
+          <t>PRAXIS LAS ESTRELLAS</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-12.06216</t>
+          <t>-12.02733</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-75.21608</t>
+          <t>-75.23433</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2318</t>
+          <t>949</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>223289</t>
+          <t>223152</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>HEROES DEL CENEPA</t>
+          <t>31942 MARISCAL CASTILLA</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-12.01819</t>
+          <t>-12.05833</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-75.22348</t>
+          <t>-75.21809</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>496</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,37 +1865,37 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>223294</t>
+          <t>223208</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE FATIMA</t>
+          <t>FRANCISCO DE ZELA</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-12.0633</t>
+          <t>-12.038</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-75.22601</t>
+          <t>-75.2225</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>446</t>
+          <t>258</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>223307</t>
+          <t>715871</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>30129 MICAELA BASTIDAS</t>
+          <t>TRILCE</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-12.05126</t>
+          <t>-12.06588</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-75.2092</t>
+          <t>-75.22164</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>621</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>223374</t>
+          <t>223091</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>EMILIA BARCIA BONIFFATTI</t>
+          <t>31510 VIRGEN DE FATIMA</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-12.0648</t>
+          <t>-12.04921</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-75.21939</t>
+          <t>-75.22697</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>338</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>223425</t>
+          <t>223128</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CONVENIO ANDRES BELLO</t>
+          <t>31594</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-12.04251</t>
+          <t>-12.04798</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-75.22614</t>
+          <t>-75.21387</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>731</t>
+          <t>417</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>223492</t>
+          <t>223029</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>GERMINAL</t>
+          <t>30224 / 30224 CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-12.06585</t>
+          <t>-12.0534</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-75.22018</t>
+          <t>-75.2085</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>391</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>223680</t>
+          <t>224415</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>PRAXIS LA ESPERANZA</t>
+          <t>MAESTRO REDENTOR</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-12.03078</t>
+          <t>-12.06205</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-75.22663</t>
+          <t>-75.21412</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>261</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>223859</t>
+          <t>223213</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>PAMER</t>
+          <t>JOSE FAUSTINO SANCHEZ CARRION</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-12.04904</t>
+          <t>-12.0273</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-75.22534</t>
+          <t>-75.22916</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>795</t>
+          <t>276</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,37 +2299,37 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>223864</t>
+          <t>223963</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>COSMOS</t>
+          <t>SAN PIO X</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-12.05454</t>
+          <t>-12.04182</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-75.21288</t>
+          <t>-75.21627</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>308</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>223883</t>
+          <t>754688</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>GELICICH</t>
+          <t>INGENIERIA INTERNACIONAL</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-12.063345</t>
+          <t>-12.05424</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-75.213314</t>
+          <t>-75.21679</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>222</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,37 +2423,37 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>223958</t>
+          <t>223294</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>SALESIANO SANTA ROSA</t>
+          <t>NUESTRA SEÑORA DE FATIMA</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-12.06624</t>
+          <t>-12.0633</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-75.215</t>
+          <t>-75.22601</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1145</t>
+          <t>446</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>223963</t>
+          <t>223048</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>SAN PIO X</t>
+          <t>30226 NUESTRA SRA.DE FATIMA</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-12.04182</t>
+          <t>-12.06378</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-75.21627</t>
+          <t>-75.22582</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>457</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>224000</t>
+          <t>223307</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>HABICH</t>
+          <t>30129 MICAELA BASTIDAS</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-12.02946</t>
+          <t>-12.05126</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-75.23436</t>
+          <t>-75.2092</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>411</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,37 +2609,37 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>224057</t>
+          <t>560001</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>INGENIERIA</t>
+          <t>SOFFIANHUM</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-12.064007</t>
+          <t>-12.06176</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-75.213252</t>
+          <t>-75.22644</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1840</t>
+          <t>44</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>224156</t>
+          <t>614810</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>SAN ANTONIO MARIA CLARET</t>
+          <t>INTEGRACION</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-12.05754</t>
+          <t>-12.05177</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-75.217269</t>
+          <t>-75.21006</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>842</t>
+          <t>204</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>224383</t>
+          <t>222968</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>SALESIANO DON BOSCO</t>
+          <t>30216 SAGRADO CORAZON DE MARIA</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-12.06793</t>
+          <t>-12.0607</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-75.21709</t>
+          <t>-75.218</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>560</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>224415</t>
+          <t>223034</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>MAESTRO REDENTOR</t>
+          <t>30225 LA ALBORADA</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-12.06205</t>
+          <t>-12.0469</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-75.21412</t>
+          <t>-75.2281</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>580</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>236809</t>
+          <t>223114</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>LAS CARMELITAS</t>
+          <t>31593 JAVIER HERAUD</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-12.04338</t>
+          <t>-12.05511</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-75.23135</t>
+          <t>-75.23259</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>394</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,37 +2919,37 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>560001</t>
+          <t>223190</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>SOFFIANHUM</t>
+          <t>MICAELA BASTIDAS</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-12.06176</t>
+          <t>-12.0503</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-75.22644</t>
+          <t>-75.2293</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>600</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>614810</t>
+          <t>223680</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>INTEGRACION</t>
+          <t>PRAXIS LA ESPERANZA</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-12.05177</t>
+          <t>-12.03078</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-75.21006</t>
+          <t>-75.22663</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>975</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3043,37 +3043,37 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>640890</t>
+          <t>223425</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>SOFFIANHUM</t>
+          <t>CONVENIO ANDRES BELLO</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-12.06177</t>
+          <t>-12.04251</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-75.22643</t>
+          <t>-75.22614</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>731</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>641093</t>
+          <t>841780</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>WINNER BOYS</t>
+          <t>HARVARD</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-12.04498</t>
+          <t>-12.052298</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-75.21403</t>
+          <t>-75.224459</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>699</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>641494</t>
+          <t>223232</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>31508 SIMON BOLIVAR</t>
+          <t>LA VICTORIA</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-12.05188</t>
+          <t>-12.02835</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-75.23397</t>
+          <t>-75.23743</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>700</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>641516</t>
+          <t>223859</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>31557 CAHUIDE</t>
+          <t>PAMER</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-12.0339</t>
+          <t>-12.04904</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-75.2272</t>
+          <t>-75.22534</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>795</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3291,32 +3291,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>642361</t>
+          <t>223883</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>LATINO INNOVA E.I.R.L.</t>
+          <t>GELICICH</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-12.03116</t>
+          <t>-12.063345</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-75.2279</t>
+          <t>-75.213314</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>614</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>43</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>715871</t>
+          <t>223958</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>TRILCE</t>
+          <t>SALESIANO SANTA ROSA</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-12.06588</t>
+          <t>-12.06624</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-75.22164</t>
+          <t>-75.215</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>1145</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>754688</t>
+          <t>224156</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>INGENIERIA INTERNACIONAL</t>
+          <t>SAN ANTONIO MARIA CLARET</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-12.05424</t>
+          <t>-12.05754</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-75.21679</t>
+          <t>-75.217269</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>842</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>46</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3477,32 +3477,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>779844</t>
+          <t>224383</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>PRAXIS LAS ESTRELLAS</t>
+          <t>SALESIANO DON BOSCO</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-12.02733</t>
+          <t>-12.06793</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-75.23433</t>
+          <t>-75.21709</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>691</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>47</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>835152</t>
+          <t>223864</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>SEMILLITAS DE HORIZONTE</t>
+          <t>COSMOS</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-12.05074</t>
+          <t>-12.05454</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-75.21549</t>
+          <t>-75.21288</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3601,37 +3601,37 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>841780</t>
+          <t>640890</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>HARVARD</t>
+          <t>SOFFIANHUM</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-12.052298</t>
+          <t>-12.06177</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-75.224459</t>
+          <t>-75.22643</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>51</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3663,32 +3663,32 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>848531</t>
+          <t>224057</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>EXCELENTI</t>
+          <t>INGENIERIA</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-12.06047</t>
+          <t>-12.064007</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-75.21357</t>
+          <t>-75.213252</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>1840</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>66</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">

--- a/ZonasEscolares/excels/JUNIN-HUANCAYO-EL_TAMBO.xlsx
+++ b/ZonasEscolares/excels/JUNIN-HUANCAYO-EL_TAMBO.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>236809</t>
+          <t>848531</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>LAS CARMELITAS</t>
+          <t>EXCELENTI</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-12.04338</t>
+          <t>705</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-75.23135</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>-12.06047</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-75.21357</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>222690</t>
+          <t>841780</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>LUIS AGUILAR ROMANI</t>
+          <t>HARVARD</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-12.05671</t>
+          <t>699</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-75.234</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>-12.052298</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>-75.224459</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,37 +625,37 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>223492</t>
+          <t>835152</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>GERMINAL</t>
+          <t>SEMILLITAS DE HORIZONTE</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-12.06585</t>
+          <t>43</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-75.22018</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>-12.05074</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-75.21549</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>641516</t>
+          <t>779844</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>31557 CAHUIDE</t>
+          <t>PRAXIS LAS ESTRELLAS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-12.0339</t>
+          <t>949</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-75.2272</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>-12.02733</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-75.23433</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>222708</t>
+          <t>754688</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>255 MI PEQUEÑO MUNDO</t>
+          <t>INGENIERIA INTERNACIONAL</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-12.0567</t>
+          <t>222</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-75.2246</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>-12.05424</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-75.21679</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>223374</t>
+          <t>715871</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>EMILIA BARCIA BONIFFATTI</t>
+          <t>TRILCE</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-12.0648</t>
+          <t>621</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-75.21939</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>-12.06588</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-75.22164</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>222987</t>
+          <t>642361</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>30218 MADRE TERESA DE CALCUTA</t>
+          <t>LATINO INNOVA E.I.R.L.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-12.03745</t>
+          <t>289</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-75.22306</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>-12.03116</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-75.2279</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>223072</t>
+          <t>641516</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>30426 VIRGEN DE LA MERCED</t>
+          <t>31557 CAHUIDE</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-12.0424</t>
+          <t>256</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-75.2207</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>-12.0339</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-75.2272</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>641093</t>
+          <t>641494</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>WINNER BOYS</t>
+          <t>31508 SIMON BOLIVAR</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-12.04498</t>
+          <t>365</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-75.21403</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>-12.05188</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-75.23397</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>848531</t>
+          <t>641093</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>EXCELENTI</t>
+          <t>WINNER BOYS</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-12.06047</t>
+          <t>558</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-75.21357</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>-12.04498</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-75.21403</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,37 +1121,37 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>223251</t>
+          <t>640890</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>POLITECNICO REGIONAL DEL CENTRO</t>
+          <t>SOFFIANHUM</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-12.06216</t>
+          <t>51</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-75.21608</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2318</t>
+          <t>-12.06177</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>-75.22643</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>221266</t>
+          <t>614810</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ICTUS CRISTO SALVADOR</t>
+          <t>INTEGRACION</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-12.06543</t>
+          <t>204</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-75.22152</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>-12.05177</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-75.21006</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,37 +1245,37 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>222727</t>
+          <t>560001</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>30211</t>
+          <t>SOFFIANHUM</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-12.0218</t>
+          <t>44</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-75.2332</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>-12.06176</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-75.22644</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>222930</t>
+          <t>236809</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>30213 / 30213 JUAN LUCIO SOTO JEREMIAS</t>
+          <t>LAS CARMELITAS</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-12.0618</t>
+          <t>218</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-75.2302</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>-12.04338</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-75.23135</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>642361</t>
+          <t>224415</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>LATINO INNOVA E.I.R.L.</t>
+          <t>MAESTRO REDENTOR</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-12.03116</t>
+          <t>261</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-75.2279</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>-12.06205</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-75.21412</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,37 +1431,37 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>222850</t>
+          <t>224383</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>SALESIANO DON BOSCO</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-12.0497</t>
+          <t>691</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-75.2146</t>
+          <t>47</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-12.06793</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-75.21709</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1493,37 +1493,37 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>835152</t>
+          <t>224156</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SEMILLITAS DE HORIZONTE</t>
+          <t>SAN ANTONIO MARIA CLARET</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-12.05074</t>
+          <t>842</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-75.21549</t>
+          <t>46</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>-12.05754</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-75.217269</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>223289</t>
+          <t>224057</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>HEROES DEL CENEPA</t>
+          <t>INGENIERIA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-12.01819</t>
+          <t>1840</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-75.22348</t>
+          <t>66</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>-12.064007</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-75.213252</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1627,22 +1627,22 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
           <t>-12.02946</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>-75.23436</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>21</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>641494</t>
+          <t>223963</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>31508 SIMON BOLIVAR</t>
+          <t>SAN PIO X</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-12.05188</t>
+          <t>308</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-75.23397</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>-12.04182</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-75.21627</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>779844</t>
+          <t>223958</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>PRAXIS LAS ESTRELLAS</t>
+          <t>SALESIANO SANTA ROSA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-12.02733</t>
+          <t>1145</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-75.23433</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>-12.06624</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-75.215</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>223152</t>
+          <t>223883</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>31942 MARISCAL CASTILLA</t>
+          <t>GELICICH</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-12.05833</t>
+          <t>614</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-75.21809</t>
+          <t>43</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>496</t>
+          <t>-12.063345</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-75.213314</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,37 +1865,37 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>223208</t>
+          <t>223864</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>FRANCISCO DE ZELA</t>
+          <t>COSMOS</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-12.038</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-75.2225</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>-12.05454</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-75.21288</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>715871</t>
+          <t>223859</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>TRILCE</t>
+          <t>PAMER</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-12.06588</t>
+          <t>795</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-75.22164</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>-12.04904</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-75.22534</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>223091</t>
+          <t>223680</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>31510 VIRGEN DE FATIMA</t>
+          <t>PRAXIS LA ESPERANZA</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-12.04921</t>
+          <t>975</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-75.22697</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>-12.03078</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-75.22663</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>223128</t>
+          <t>223492</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>31594</t>
+          <t>GERMINAL</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-12.04798</t>
+          <t>494</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-75.21387</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>417</t>
+          <t>-12.06585</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-75.22018</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>223029</t>
+          <t>223425</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>30224 / 30224 CORAZON DE JESUS</t>
+          <t>CONVENIO ANDRES BELLO</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-12.0534</t>
+          <t>731</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-75.2085</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>-12.04251</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-75.22614</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>224415</t>
+          <t>223374</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>MAESTRO REDENTOR</t>
+          <t>EMILIA BARCIA BONIFFATTI</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-12.06205</t>
+          <t>220</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-75.21412</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>-12.0648</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-75.21939</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>223213</t>
+          <t>223307</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>JOSE FAUSTINO SANCHEZ CARRION</t>
+          <t>30129 MICAELA BASTIDAS</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-12.0273</t>
+          <t>411</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-75.22916</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>-12.05126</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-75.2092</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,37 +2299,37 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>223963</t>
+          <t>223294</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>SAN PIO X</t>
+          <t>NUESTRA SEÑORA DE FATIMA</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-12.04182</t>
+          <t>446</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-75.21627</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>-12.0633</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-75.22601</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>754688</t>
+          <t>223289</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>INGENIERIA INTERNACIONAL</t>
+          <t>HEROES DEL CENEPA</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-12.05424</t>
+          <t>251</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-75.21679</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>-12.01819</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-75.22348</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,37 +2423,37 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>223294</t>
+          <t>223251</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE FATIMA</t>
+          <t>POLITECNICO REGIONAL DEL CENTRO</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-12.0633</t>
+          <t>2318</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-75.22601</t>
+          <t>152</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>446</t>
+          <t>-12.06216</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-75.21608</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>223048</t>
+          <t>223232</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>30226 NUESTRA SRA.DE FATIMA</t>
+          <t>LA VICTORIA</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-12.06378</t>
+          <t>700</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-75.22582</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>457</t>
+          <t>-12.02835</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-75.23743</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>223307</t>
+          <t>223213</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>30129 MICAELA BASTIDAS</t>
+          <t>JOSE FAUSTINO SANCHEZ CARRION</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-12.05126</t>
+          <t>276</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-75.2092</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>-12.0273</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-75.22916</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,37 +2609,37 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>560001</t>
+          <t>223208</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>SOFFIANHUM</t>
+          <t>FRANCISCO DE ZELA</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-12.06176</t>
+          <t>258</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-75.22644</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>-12.038</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-75.2225</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>614810</t>
+          <t>223190</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>INTEGRACION</t>
+          <t>MICAELA BASTIDAS</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-12.05177</t>
+          <t>600</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-75.21006</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>-12.0503</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-75.2293</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>222968</t>
+          <t>223152</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>30216 SAGRADO CORAZON DE MARIA</t>
+          <t>31942 MARISCAL CASTILLA</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-12.0607</t>
+          <t>496</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-75.218</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>-12.05833</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-75.21809</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>223034</t>
+          <t>223128</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>30225 LA ALBORADA</t>
+          <t>31594</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-12.0469</t>
+          <t>417</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-75.2281</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>-12.04798</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-75.21387</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2867,22 +2867,22 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
+          <t>394</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
           <t>-12.05511</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>-75.23259</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>394</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>31</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>223190</t>
+          <t>223091</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>MICAELA BASTIDAS</t>
+          <t>31510 VIRGEN DE FATIMA</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-12.0503</t>
+          <t>338</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-75.2293</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>-12.04921</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-75.22697</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>223680</t>
+          <t>223072</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>PRAXIS LA ESPERANZA</t>
+          <t>30426 VIRGEN DE LA MERCED</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-12.03078</t>
+          <t>299</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-75.22663</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>-12.0424</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>-75.2207</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>223425</t>
+          <t>223048</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>CONVENIO ANDRES BELLO</t>
+          <t>30226 NUESTRA SRA.DE FATIMA</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-12.04251</t>
+          <t>457</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-75.22614</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>731</t>
+          <t>-12.06378</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>-75.22582</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>841780</t>
+          <t>223034</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>HARVARD</t>
+          <t>30225 LA ALBORADA</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-12.052298</t>
+          <t>580</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-75.224459</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>-12.0469</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>-75.2281</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>223232</t>
+          <t>223029</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>LA VICTORIA</t>
+          <t>30224 / 30224 CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-12.02835</t>
+          <t>391</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-75.23743</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>-12.0534</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>-75.2085</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>223859</t>
+          <t>222987</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>PAMER</t>
+          <t>30218 MADRE TERESA DE CALCUTA</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-12.04904</t>
+          <t>266</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-75.22534</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>795</t>
+          <t>-12.03745</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-75.22306</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3291,32 +3291,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>223883</t>
+          <t>222968</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>GELICICH</t>
+          <t>30216 SAGRADO CORAZON DE MARIA</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-12.063345</t>
+          <t>560</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-75.213314</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>-12.0607</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>-75.218</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>223958</t>
+          <t>222930</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>SALESIANO SANTA ROSA</t>
+          <t>30213 / 30213 JUAN LUCIO SOTO JEREMIAS</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-12.06624</t>
+          <t>333</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-75.215</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1145</t>
+          <t>-12.0618</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>-75.2302</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3415,37 +3415,37 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>224156</t>
+          <t>222850</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>SAN ANTONIO MARIA CLARET</t>
+          <t>643</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-12.05754</t>
+          <t>28</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-75.217269</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>842</t>
+          <t>-12.0497</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>-75.2146</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3477,32 +3477,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>224383</t>
+          <t>222727</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>SALESIANO DON BOSCO</t>
+          <t>30211</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-12.06793</t>
+          <t>350</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-75.21709</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>-12.0218</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>-75.2332</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3539,37 +3539,37 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>223864</t>
+          <t>222708</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>COSMOS</t>
+          <t>255 MI PEQUEÑO MUNDO</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-12.05454</t>
+          <t>280</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-75.21288</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-12.0567</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>-75.2246</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3601,37 +3601,37 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>640890</t>
+          <t>222690</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>SOFFIANHUM</t>
+          <t>LUIS AGUILAR ROMANI</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-12.06177</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-75.22643</t>
+          <t>101</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>-12.05671</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>-75.234</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3663,32 +3663,32 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>224057</t>
+          <t>221266</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>INGENIERIA</t>
+          <t>ICTUS CRISTO SALVADOR</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-12.064007</t>
+          <t>202</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-75.213252</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1840</t>
+          <t>-12.06543</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>-75.22152</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">

--- a/ZonasEscolares/excels/JUNIN-HUANCAYO-EL_TAMBO.xlsx
+++ b/ZonasEscolares/excels/JUNIN-HUANCAYO-EL_TAMBO.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
